--- a/data/availability/projects/al-ahly-sabbour/gaia.xlsx
+++ b/data/availability/projects/al-ahly-sabbour/gaia.xlsx
@@ -457,16 +457,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Template for Gaia</t>
+          <t>Live inventory for gaia</t>
         </is>
       </c>
     </row>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,6 +543,56 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>payment_plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gaia</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>265</v>
+      </c>
+      <c r="F2" t="n">
+        <v>265</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="H2" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5% down payment over 7 years equal installments</t>
         </is>
       </c>
     </row>
@@ -557,7 +607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -624,6 +674,67 @@
       <c r="M1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>gaia</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Standalone Villa</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>L6-L6</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Finished</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>265</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Floor: GRD | Garden: 229.0 sqm</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Landscape</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>47670000</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2027</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>5% down payment over 7 years equal installments</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Available</t>
         </is>
       </c>
     </row>

--- a/data/availability/projects/al-ahly-sabbour/gaia.xlsx
+++ b/data/availability/projects/al-ahly-sabbour/gaia.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>delivery_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Inventory for gaia-ras-el-hekma</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
